--- a/data/trans_orig/IP39B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP39B-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>18320</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>31429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13178</t>
+          <t>13017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34725</t>
+          <t>34709</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52959</t>
+          <t>52355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45712</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60259</t>
+          <t>60797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44693</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57668</t>
+          <t>57286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94408</t>
+          <t>95310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114531</t>
+          <t>114932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,07%</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45893</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54733</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42195</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52730</t>
+          <t>53072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93178</t>
+          <t>92082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105893</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22642</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40104</t>
+          <t>40812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35279</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37963</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>50704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>82137</t>
+          <t>82385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24722</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101623</t>
+          <t>102328</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113253</t>
+          <t>113627</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>106036</t>
+          <t>105776</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115594</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>212248</t>
+          <t>211654</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>226552</t>
+          <t>226299</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>511</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45177</t>
+          <t>45185</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>53500</t>
+          <t>54053</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59930</t>
+          <t>59938</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>97239</t>
+          <t>97575</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104490</t>
+          <t>104442</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>96963</t>
+          <t>97791</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129354</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>278715</t>
+          <t>278170</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>303646</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>303552</t>
+          <t>302472</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>326633</t>
+          <t>327219</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>589580</t>
+          <t>588313</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>624468</t>
+          <t>623294</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33261</t>
+          <t>33581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34486</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47722</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43607</t>
+          <t>44110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56049</t>
+          <t>55936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83258</t>
+          <t>83056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100282</t>
+          <t>100745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39355</t>
+          <t>39072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48621</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41368</t>
+          <t>41612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50962</t>
+          <t>50839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83790</t>
+          <t>84111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97806</t>
+          <t>97430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39663</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>48379</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>29906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>39882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72601</t>
+          <t>72369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85841</t>
+          <t>85949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18569</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70483</t>
+          <t>71371</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79965</t>
+          <t>80307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>83634</t>
+          <t>83492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>95168</t>
+          <t>95338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>158700</t>
+          <t>157221</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>173704</t>
+          <t>173190</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52044</t>
+          <t>52030</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39040</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>46238</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>88439</t>
+          <t>89304</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>97177</t>
+          <t>97323</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>28138</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>67471</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>95253</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>249229</t>
+          <t>248741</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>271182</t>
+          <t>271594</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>262098</t>
+          <t>262097</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>284226</t>
+          <t>285319</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>517267</t>
+          <t>518936</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>551568</t>
+          <t>551817</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46953</t>
+          <t>45968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57081</t>
+          <t>56833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54251</t>
+          <t>53675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65646</t>
+          <t>65743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103582</t>
+          <t>104382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119877</t>
+          <t>119797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49361</t>
+          <t>49215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58862</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55310</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65486</t>
+          <t>64843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107681</t>
+          <t>107424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121542</t>
+          <t>121074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11349</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>31525</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33217</t>
+          <t>33179</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>42518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58944</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71143</t>
+          <t>71576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14222</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90211</t>
+          <t>89546</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>102763</t>
+          <t>102152</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98982</t>
+          <t>98909</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>108039</t>
+          <t>108480</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>192690</t>
+          <t>192599</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>207357</t>
+          <t>208584</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>47590</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>51826</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>52256</t>
+          <t>52173</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57196</t>
+          <t>57199</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>102174</t>
+          <t>102180</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>108722</t>
+          <t>108771</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>57332</t>
+          <t>58119</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>276656</t>
+          <t>274531</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>295781</t>
+          <t>295688</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>309397</t>
+          <t>308410</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>329914</t>
+          <t>331188</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>590035</t>
+          <t>588387</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>620637</t>
+          <t>620559</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
